--- a/models/organization.xlsx
+++ b/models/organization.xlsx
@@ -8,24 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/rbac/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{038E3EA7-DB94-9843-BE8F-3F1D20CC5FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91BE2CC4-6673-7B4F-877E-6BB7AB478D61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="700" windowWidth="27040" windowHeight="15540" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33380" yWindow="18500" windowWidth="27040" windowHeight="15540" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" r:id="rId1"/>
     <sheet name="fields" sheetId="2" r:id="rId2"/>
     <sheet name="validation" sheetId="3" r:id="rId3"/>
-    <sheet name="codes" sheetId="6" r:id="rId4"/>
-    <sheet name="coding" sheetId="4" r:id="rId5"/>
-    <sheet name="help" sheetId="5" r:id="rId6"/>
+    <sheet name="data" sheetId="7" r:id="rId4"/>
+    <sheet name="codes" sheetId="6" r:id="rId5"/>
+    <sheet name="coding" sheetId="4" r:id="rId6"/>
+    <sheet name="help" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="123">
   <si>
     <t>name</t>
   </si>
@@ -395,6 +396,14 @@
   </si>
   <si>
     <t>parentid='distinct'</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>platform</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -488,7 +497,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -519,6 +528,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1214,6 +1226,33 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE51EC43-9077-E94C-AB4B-751E213AB89C}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F320EF-9F36-7343-A80F-204E30BFE363}">
   <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
@@ -1299,7 +1338,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
@@ -1427,7 +1466,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>

--- a/models/organization.xlsx
+++ b/models/organization.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/rbac/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91BE2CC4-6673-7B4F-877E-6BB7AB478D61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBA9EBF0-7E6B-584B-AB19-FE60289AA81E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33380" yWindow="18500" windowWidth="27040" windowHeight="15540" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="25100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="125">
   <si>
     <t>name</t>
   </si>
@@ -170,12 +170,6 @@
   </si>
   <si>
     <t>0:业主机构；1:分销商；2:公司客户；3:个人客户；4：供应商</t>
-  </si>
-  <si>
-    <t>accountid</t>
-  </si>
-  <si>
-    <t>账号</t>
   </si>
   <si>
     <t>timestamp</t>
@@ -404,6 +398,22 @@
   </si>
   <si>
     <t>0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>idx1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>unique:orgname</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sitename</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>网站域名</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -497,7 +507,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -526,12 +536,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1102,7 +1113,7 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>44</v>
@@ -1132,17 +1143,17 @@
       </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>49</v>
+      <c r="A18" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="C18" t="s">
         <v>14</v>
       </c>
       <c r="D18">
-        <v>32</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -1177,15 +1188,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="5"/>
-      <c r="C2" s="5"/>
+      <c r="A2" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="5"/>
@@ -1239,11 +1257,11 @@
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="11" t="s">
-        <v>122</v>
+      <c r="A2" s="10" t="s">
+        <v>120</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -1263,22 +1281,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>108</v>
-      </c>
       <c r="F1" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1286,50 +1304,50 @@
         <v>23</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>116</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -1345,118 +1363,118 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" t="s">
         <v>53</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>54</v>
-      </c>
-      <c r="C1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" t="s">
         <v>57</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" t="s">
         <v>60</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
         <v>61</v>
-      </c>
-      <c r="C3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D3" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" t="s">
         <v>64</v>
-      </c>
-      <c r="B4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="B11" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="B12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="B13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1479,14 +1497,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="D1" s="10"/>
+      <c r="A1" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="11"/>
       <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
@@ -1496,114 +1514,114 @@
         <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>83</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>88</v>
       </c>
       <c r="E3" s="4"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="E4" s="4"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E5" s="4"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E6" s="4"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E7" s="4"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>98</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>100</v>
       </c>
       <c r="E8" s="4"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
@@ -1611,10 +1629,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
@@ -1622,10 +1640,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
@@ -1633,10 +1651,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>

--- a/models/organization.xlsx
+++ b/models/organization.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/rbac/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBA9EBF0-7E6B-584B-AB19-FE60289AA81E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3DF47D6-E2F3-B34C-92DF-81548815433D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="25100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="128">
   <si>
     <t>name</t>
   </si>
@@ -414,6 +414,18 @@
   </si>
   <si>
     <t>网站域名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>orgabbr</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>机构简称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>str</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -539,10 +551,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -870,7 +882,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="16.1640625" customWidth="1"/>
@@ -931,18 +943,18 @@
         <v>14</v>
       </c>
       <c r="D3">
-        <v>100</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
+      <c r="A4" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>127</v>
       </c>
       <c r="D4">
         <v>100</v>
@@ -950,52 +962,52 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6">
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7">
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="5" t="s">
+    <row r="8" spans="1:8">
+      <c r="A8" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B8" s="7" t="s">
         <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>26</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
@@ -1006,10 +1018,10 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>
@@ -1020,86 +1032,83 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
       </c>
       <c r="D10">
-        <v>256</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
       </c>
       <c r="D11">
-        <v>400</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
       </c>
       <c r="D12">
-        <v>1000</v>
+        <v>400</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
         <v>14</v>
       </c>
       <c r="D13">
-        <v>100</v>
-      </c>
-      <c r="H13" t="s">
-        <v>37</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
         <v>14</v>
       </c>
       <c r="D14">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="H14" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
         <v>14</v>
@@ -1108,29 +1117,32 @@
         <v>400</v>
       </c>
       <c r="H15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16">
+        <v>400</v>
+      </c>
+      <c r="H16" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="9" t="s">
+    <row r="17" spans="1:8">
+      <c r="A17" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B17" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="C16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>46</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
@@ -1138,21 +1150,35 @@
       <c r="D17">
         <v>32</v>
       </c>
-      <c r="H17" t="s">
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18">
+        <v>32</v>
+      </c>
+      <c r="H18" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="9" t="s">
+    <row r="19" spans="1:8">
+      <c r="A19" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B19" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="C18" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18">
+      <c r="C19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19">
         <v>300</v>
       </c>
     </row>
@@ -1167,7 +1193,7 @@
           <x14:formula1>
             <xm:f>coding!$B$2:$B$12</xm:f>
           </x14:formula1>
-          <xm:sqref>C4 C2:C3 C5:C18 C19:C339</xm:sqref>
+          <xm:sqref>C5 C2:C4 C6:C19 C20:C340</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1497,14 +1523,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="11"/>
+      <c r="D1" s="12"/>
       <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
